--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomislav\Desktop\rasadnik\rasadnik-bernat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8470BFE-BEF1-478C-A953-B3ACA2B5A04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D8724D-F094-46F4-9F3A-23447BFBBAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contact" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
   <si>
     <t>number</t>
   </si>
@@ -186,12 +186,6 @@
     <t>https://maps.app.goo.gl/WrfEUjHcn54o7LMY7</t>
   </si>
   <si>
-    <t>5 EUR</t>
-  </si>
-  <si>
-    <t>7 EUR</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 'Seedling information:
 - One-year-old red oak seedlings. Seedling height 70-100cm
@@ -309,12 +303,6 @@
 - Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
   </si>
   <si>
-    <t>9 EUR</t>
-  </si>
-  <si>
-    <t>15 EUR</t>
-  </si>
-  <si>
     <t>crvenolisni_hrast_golog_korjena_70_100</t>
   </si>
   <si>
@@ -351,9 +339,6 @@
   </si>
   <si>
     <t>hrast_kitnjak_golog_korjena_100_150</t>
-  </si>
-  <si>
-    <t>TRENUTNO NEDOSTUPNO</t>
   </si>
   <si>
     <t>Informacije o sadnicama:
@@ -450,12 +435,15 @@
 - Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
 - Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, i odgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
   </si>
+  <si>
+    <t>anchorPrice</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -473,14 +461,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -517,7 +497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -542,13 +522,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hiperveza" xfId="1" builtinId="8"/>
-    <cellStyle name="Normalno" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -765,16 +745,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" customWidth="1"/>
-    <col min="5" max="5" width="365.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" customWidth="1"/>
+    <col min="5" max="5" width="365.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -791,7 +771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
@@ -822,17 +802,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" customWidth="1"/>
-    <col min="2" max="2" width="47.109375" customWidth="1"/>
-    <col min="3" max="4" width="170.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" customWidth="1"/>
-    <col min="6" max="6" width="45.109375" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
+    <col min="3" max="4" width="170.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.85546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="45.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -845,171 +825,198 @@
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="194.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="13">
+        <v>5</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="186.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="13">
+        <v>7</v>
+      </c>
+      <c r="F3" s="13">
+        <v>7</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="166.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="13">
+        <v>5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>5</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="176.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="13">
+        <v>9</v>
+      </c>
+      <c r="F5" s="13">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="176.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="E6" s="13">
+        <v>15</v>
+      </c>
+      <c r="F6" s="13">
+        <v>15</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="7" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="172.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="172.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="172.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="172.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="E9" s="13">
+        <v>4</v>
+      </c>
+      <c r="F9" s="13">
+        <v>4</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1023,16 +1030,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="4" width="55.6640625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" customWidth="1"/>
-    <col min="6" max="30" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="4" width="55.7109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="30" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1049,7 +1056,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="363" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="363" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1066,21 +1073,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="11"/>
@@ -1098,16 +1105,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="66.44140625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="70.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="66.42578125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="70.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,7 +1131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -1141,7 +1148,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
@@ -1158,7 +1165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
